--- a/output/roomself_excel/9421.xlsx
+++ b/output/roomself_excel/9421.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>145079</v>
+        <v>39410</v>
       </c>
       <c r="D2" t="n">
-        <v>5504</v>
+        <v>1732</v>
       </c>
       <c r="E2" t="n">
-        <v>1094</v>
+        <v>232</v>
       </c>
       <c r="F2" t="n">
-        <v>125</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>105444</v>
+        <v>135616</v>
       </c>
       <c r="D3" t="n">
-        <v>3108</v>
+        <v>3260</v>
       </c>
       <c r="E3" t="n">
-        <v>338</v>
+        <v>523</v>
       </c>
       <c r="F3" t="n">
-        <v>305</v>
+        <v>325</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12654</v>
+        <v>248132</v>
       </c>
       <c r="D4" t="n">
-        <v>900</v>
+        <v>4104</v>
       </c>
       <c r="E4" t="n">
-        <v>111</v>
+        <v>647</v>
       </c>
       <c r="F4" t="n">
-        <v>16</v>
+        <v>414</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>248132</v>
+        <v>105444</v>
       </c>
       <c r="D5" t="n">
-        <v>4104</v>
+        <v>3108</v>
       </c>
       <c r="E5" t="n">
-        <v>1112</v>
+        <v>338</v>
       </c>
       <c r="F5" t="n">
-        <v>414</v>
+        <v>305</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>175174</v>
+        <v>21840</v>
       </c>
       <c r="D6" t="n">
-        <v>4164</v>
+        <v>1252</v>
       </c>
       <c r="E6" t="n">
-        <v>705</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>336</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -576,14 +576,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>204798</v>
+        <v>31312</v>
       </c>
       <c r="D7" t="n">
-        <v>3808</v>
+        <v>1548</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -602,16 +602,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21840</v>
+        <v>67099</v>
       </c>
       <c r="D8" t="n">
-        <v>1252</v>
+        <v>2360</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>135616</v>
+        <v>28620</v>
       </c>
       <c r="D9" t="n">
-        <v>3260</v>
+        <v>1356</v>
       </c>
       <c r="E9" t="n">
-        <v>523</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>325</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>46565</v>
+        <v>217453</v>
       </c>
       <c r="D10" t="n">
-        <v>1896</v>
+        <v>4184</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>975</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>323</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>31312</v>
+        <v>145079</v>
       </c>
       <c r="D11" t="n">
-        <v>1548</v>
+        <v>5504</v>
       </c>
       <c r="E11" t="n">
-        <v>430</v>
+        <v>1094</v>
       </c>
       <c r="F11" t="n">
-        <v>16</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12">
@@ -690,16 +690,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>112282</v>
+        <v>12654</v>
       </c>
       <c r="D12" t="n">
-        <v>4000</v>
+        <v>900</v>
       </c>
       <c r="E12" t="n">
-        <v>383</v>
+        <v>111</v>
       </c>
       <c r="F12" t="n">
-        <v>338</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
@@ -712,16 +712,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>138026</v>
+        <v>135764</v>
       </c>
       <c r="D13" t="n">
-        <v>3116</v>
+        <v>3188</v>
       </c>
       <c r="E13" t="n">
-        <v>548</v>
+        <v>494</v>
       </c>
       <c r="F13" t="n">
-        <v>404</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14">
@@ -734,16 +734,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>52257</v>
+        <v>204798</v>
       </c>
       <c r="D14" t="n">
-        <v>2272</v>
+        <v>3808</v>
       </c>
       <c r="E14" t="n">
-        <v>467</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>195</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -756,16 +756,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>62185</v>
+        <v>46565</v>
       </c>
       <c r="D15" t="n">
-        <v>2616</v>
+        <v>1896</v>
       </c>
       <c r="E15" t="n">
-        <v>709</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>154</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -778,16 +778,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>53352</v>
+        <v>112282</v>
       </c>
       <c r="D16" t="n">
-        <v>1932</v>
+        <v>4000</v>
       </c>
       <c r="E16" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -800,16 +800,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>103290</v>
+        <v>138026</v>
       </c>
       <c r="D17" t="n">
-        <v>3164</v>
+        <v>3116</v>
       </c>
       <c r="E17" t="n">
-        <v>626</v>
+        <v>548</v>
       </c>
       <c r="F17" t="n">
-        <v>9</v>
+        <v>404</v>
       </c>
     </row>
     <row r="18">
@@ -818,20 +818,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>217453</v>
+        <v>52257</v>
       </c>
       <c r="D18" t="n">
-        <v>4184</v>
+        <v>2272</v>
       </c>
       <c r="E18" t="n">
-        <v>975</v>
+        <v>190</v>
       </c>
       <c r="F18" t="n">
-        <v>323</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19">
@@ -844,16 +844,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>38036</v>
+        <v>62185</v>
       </c>
       <c r="D19" t="n">
-        <v>1620</v>
+        <v>2616</v>
       </c>
       <c r="E19" t="n">
-        <v>148</v>
+        <v>384</v>
       </c>
       <c r="F19" t="n">
-        <v>39</v>
+        <v>139</v>
       </c>
     </row>
     <row r="20">
@@ -862,20 +862,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>67099</v>
+        <v>53352</v>
       </c>
       <c r="D20" t="n">
-        <v>2360</v>
+        <v>1932</v>
       </c>
       <c r="E20" t="n">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="F20" t="n">
-        <v>187</v>
+        <v>180</v>
       </c>
     </row>
     <row r="21">
@@ -888,16 +888,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>99981</v>
+        <v>103290</v>
       </c>
       <c r="D21" t="n">
-        <v>2944</v>
+        <v>3164</v>
       </c>
       <c r="E21" t="n">
-        <v>406</v>
+        <v>626</v>
       </c>
       <c r="F21" t="n">
-        <v>402</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22">
@@ -906,20 +906,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>28620</v>
+        <v>38036</v>
       </c>
       <c r="D22" t="n">
-        <v>1356</v>
+        <v>1620</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23">
@@ -932,16 +932,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>24393</v>
+        <v>99981</v>
       </c>
       <c r="D23" t="n">
-        <v>1404</v>
+        <v>2944</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>406</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>402</v>
       </c>
     </row>
     <row r="24">
@@ -954,16 +954,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>80414</v>
+        <v>24393</v>
       </c>
       <c r="D24" t="n">
-        <v>3544</v>
+        <v>1404</v>
       </c>
       <c r="E24" t="n">
-        <v>975</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>433</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -976,16 +976,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>91275</v>
+        <v>80414</v>
       </c>
       <c r="D25" t="n">
-        <v>3620</v>
+        <v>3544</v>
       </c>
       <c r="E25" t="n">
-        <v>698</v>
+        <v>551</v>
       </c>
       <c r="F25" t="n">
-        <v>177</v>
+        <v>433</v>
       </c>
     </row>
     <row r="26">
@@ -998,16 +998,38 @@
         </is>
       </c>
       <c r="C26" t="n">
+        <v>91275</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3620</v>
+      </c>
+      <c r="E26" t="n">
+        <v>376</v>
+      </c>
+      <c r="F26" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
         <v>98174</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D27" t="n">
         <v>2556</v>
       </c>
-      <c r="E26" t="n">
-        <v>832</v>
-      </c>
-      <c r="F26" t="n">
+      <c r="E27" t="n">
         <v>401</v>
+      </c>
+      <c r="F27" t="n">
+        <v>294</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/9421.xlsx
+++ b/output/roomself_excel/9421.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
         </is>
       </c>
     </row>
@@ -475,12 +510,15 @@
       <c r="D2" t="n">
         <v>1732</v>
       </c>
-      <c r="E2" t="n">
-        <v>232</v>
-      </c>
-      <c r="F2" t="n">
-        <v>16</v>
-      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +535,31 @@
       <c r="D3" t="n">
         <v>3260</v>
       </c>
-      <c r="E3" t="n">
-        <v>523</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>325</v>
-      </c>
+        <v>508</v>
+      </c>
+      <c r="G3" t="n">
+        <v>18</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>307</v>
+      </c>
+      <c r="J3" t="n">
+        <v>15</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +576,31 @@
       <c r="D4" t="n">
         <v>4104</v>
       </c>
-      <c r="E4" t="n">
-        <v>647</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>414</v>
-      </c>
+        <v>628</v>
+      </c>
+      <c r="G4" t="n">
+        <v>16</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>398</v>
+      </c>
+      <c r="J4" t="n">
+        <v>19</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +617,31 @@
       <c r="D5" t="n">
         <v>3108</v>
       </c>
-      <c r="E5" t="n">
-        <v>338</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>305</v>
-      </c>
+        <v>304</v>
+      </c>
+      <c r="G5" t="n">
+        <v>16</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>284</v>
+      </c>
+      <c r="J5" t="n">
+        <v>18</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +658,15 @@
       <c r="D6" t="n">
         <v>1252</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +683,15 @@
       <c r="D7" t="n">
         <v>1548</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +708,23 @@
       <c r="D8" t="n">
         <v>2360</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>169</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>39</v>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +741,15 @@
       <c r="D9" t="n">
         <v>1356</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,11 +766,38 @@
       <c r="D10" t="n">
         <v>4184</v>
       </c>
-      <c r="E10" t="n">
-        <v>975</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>323</v>
+        <v>286</v>
+      </c>
+      <c r="G10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>757</v>
+      </c>
+      <c r="J10" t="n">
+        <v>36</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>285</v>
+      </c>
+      <c r="M10" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="11">
@@ -673,11 +815,38 @@
       <c r="D11" t="n">
         <v>5504</v>
       </c>
-      <c r="E11" t="n">
-        <v>1094</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>125</v>
+        <v>1085</v>
+      </c>
+      <c r="G11" t="n">
+        <v>8</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>117</v>
+      </c>
+      <c r="J11" t="n">
+        <v>9</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>126</v>
+      </c>
+      <c r="M11" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -695,12 +864,23 @@
       <c r="D12" t="n">
         <v>900</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>111</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>16</v>
       </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +897,23 @@
       <c r="D13" t="n">
         <v>3188</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>494</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>18</v>
       </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +930,23 @@
       <c r="D14" t="n">
         <v>3808</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
-      </c>
+        <v>493</v>
+      </c>
+      <c r="G14" t="n">
+        <v>15</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +963,15 @@
       <c r="D15" t="n">
         <v>1896</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +988,15 @@
       <c r="D16" t="n">
         <v>4000</v>
       </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,12 +1013,31 @@
       <c r="D17" t="n">
         <v>3116</v>
       </c>
-      <c r="E17" t="n">
-        <v>548</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F17" t="n">
-        <v>404</v>
-      </c>
+        <v>393</v>
+      </c>
+      <c r="G17" t="n">
+        <v>19</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>384</v>
+      </c>
+      <c r="J17" t="n">
+        <v>15</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,12 +1054,23 @@
       <c r="D18" t="n">
         <v>2272</v>
       </c>
-      <c r="E18" t="n">
-        <v>190</v>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F18" t="n">
-        <v>131</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="G18" t="n">
+        <v>15</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,11 +1087,38 @@
       <c r="D19" t="n">
         <v>2616</v>
       </c>
-      <c r="E19" t="n">
-        <v>384</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F19" t="n">
-        <v>139</v>
+        <v>123</v>
+      </c>
+      <c r="G19" t="n">
+        <v>18</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>123</v>
+      </c>
+      <c r="J19" t="n">
+        <v>19</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>347</v>
+      </c>
+      <c r="M19" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="20">
@@ -871,12 +1136,31 @@
       <c r="D20" t="n">
         <v>1932</v>
       </c>
-      <c r="E20" t="n">
-        <v>321</v>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F20" t="n">
-        <v>180</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="G20" t="n">
+        <v>9</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>312</v>
+      </c>
+      <c r="J20" t="n">
+        <v>9</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -893,12 +1177,31 @@
       <c r="D21" t="n">
         <v>3164</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>165</v>
+      </c>
+      <c r="G21" t="n">
+        <v>8</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
         <v>626</v>
       </c>
-      <c r="F21" t="n">
+      <c r="J21" t="n">
         <v>9</v>
       </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -915,12 +1218,23 @@
       <c r="D22" t="n">
         <v>1620</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
         <v>148</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>39</v>
       </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -937,12 +1251,31 @@
       <c r="D23" t="n">
         <v>2944</v>
       </c>
-      <c r="E23" t="n">
-        <v>406</v>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F23" t="n">
-        <v>402</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="G23" t="n">
+        <v>39</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>367</v>
+      </c>
+      <c r="J23" t="n">
+        <v>33</v>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -959,12 +1292,15 @@
       <c r="D24" t="n">
         <v>1404</v>
       </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -981,12 +1317,23 @@
       <c r="D25" t="n">
         <v>3544</v>
       </c>
-      <c r="E25" t="n">
-        <v>551</v>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F25" t="n">
-        <v>433</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="G25" t="n">
+        <v>33</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1003,11 +1350,38 @@
       <c r="D26" t="n">
         <v>3620</v>
       </c>
-      <c r="E26" t="n">
-        <v>376</v>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F26" t="n">
-        <v>143</v>
+        <v>108</v>
+      </c>
+      <c r="G26" t="n">
+        <v>32</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>105</v>
+      </c>
+      <c r="J26" t="n">
+        <v>22</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>322</v>
+      </c>
+      <c r="M26" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="27">
@@ -1025,12 +1399,31 @@
       <c r="D27" t="n">
         <v>2556</v>
       </c>
-      <c r="E27" t="n">
-        <v>401</v>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F27" t="n">
-        <v>294</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="G27" t="n">
+        <v>19</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>382</v>
+      </c>
+      <c r="J27" t="n">
+        <v>37</v>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/roomself_excel/9421.xlsx
+++ b/output/roomself_excel/9421.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,6 +492,66 @@
       <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ExtWallWidth_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_2</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_2</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_2</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_2</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_3</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_3</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_3</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_3</t>
         </is>
       </c>
     </row>
@@ -519,6 +579,18 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -560,6 +632,42 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>430</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>18</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>200</v>
+      </c>
+      <c r="U3" t="n">
+        <v>15</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -601,6 +709,42 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>281</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>16</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>200</v>
+      </c>
+      <c r="U4" t="n">
+        <v>19</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -642,6 +786,30 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>174</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>16</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -667,6 +835,18 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -692,6 +872,18 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -725,6 +917,30 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>39</v>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -750,6 +966,18 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -799,6 +1027,54 @@
       <c r="M10" t="n">
         <v>37</v>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>266</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>39</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="T10" t="n">
+        <v>201</v>
+      </c>
+      <c r="U10" t="n">
+        <v>36</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -848,6 +1124,18 @@
       <c r="M11" t="n">
         <v>7</v>
       </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -881,6 +1169,30 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>76</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>16</v>
+      </c>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -914,6 +1226,30 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>395</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>18</v>
+      </c>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -947,6 +1283,30 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>226</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>15</v>
+      </c>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -972,6 +1332,18 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -997,6 +1369,18 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1038,6 +1422,30 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>198</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>19</v>
+      </c>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1071,6 +1479,18 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1120,6 +1540,42 @@
       <c r="M19" t="n">
         <v>16</v>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>91</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>19</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="T19" t="n">
+        <v>310</v>
+      </c>
+      <c r="U19" t="n">
+        <v>16</v>
+      </c>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1161,6 +1617,18 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1202,6 +1670,18 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1235,6 +1715,30 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>115</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>39</v>
+      </c>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1276,6 +1780,42 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>168</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>39</v>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="T23" t="n">
+        <v>165</v>
+      </c>
+      <c r="U23" t="n">
+        <v>33</v>
+      </c>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1301,6 +1841,18 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1334,6 +1886,30 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>81</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>33</v>
+      </c>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1383,6 +1959,30 @@
       <c r="M26" t="n">
         <v>35</v>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>94</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>22</v>
+      </c>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1424,6 +2024,30 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>147</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>19</v>
+      </c>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
